--- a/src/templates/statistics-template.xlsx
+++ b/src/templates/statistics-template.xlsx
@@ -2,82 +2,42 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEPTOP\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4AA300E-FA64-4DC7-8D12-C752B7311E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04CA7C68-9118-4630-AAD0-49DBC4B9AC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
-    <sheet name="Data" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Data" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_statisticstemplate.xlsxTable1" hidden="1">Table1[]</definedName>
-  </definedNames>
   <calcPr calcId="162913"/>
+  <pivotCaches>
+    <pivotCache cacheId="4" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{841E416B-1EF1-43b6-AB56-02D37102CBD5}">
-      <x15:pivotCaches>
-        <pivotCache cacheId="11" r:id="rId3"/>
-      </x15:pivotCaches>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{983426D0-5260-488c-9760-48F4B6AC55F4}">
-      <x15:pivotTableReferences>
-        <x15:pivotTableReference r:id="rId4"/>
-      </x15:pivotTableReferences>
-    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
-      <x15:dataModel>
-        <x15:modelTables>
-          <x15:modelTable id="Table1" name="Table1" connection="WorksheetConnection_statistics-template.xlsx!Table1"/>
-        </x15:modelTables>
-      </x15:dataModel>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{55235C92-B416-47AC-998D-DBB575D6D885}" keepAlive="1" name="ThisWorkbookDataModel" description="Data Model" type="5" refreshedVersion="8" minRefreshableVersion="5" background="1">
-    <dbPr connection="Data Model Connection" command="Model" commandType="1"/>
-    <olapPr sendLocale="1" rowDrillCount="1000"/>
-    <extLst>
-      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
-        <x15:connection id="" model="1"/>
-      </ext>
-    </extLst>
-  </connection>
-  <connection id="2" xr16:uid="{6A34CBFE-A21A-41EC-A81A-1A702AE2D10B}" name="WorksheetConnection_statistics-template.xlsx!Table1" type="102" refreshedVersion="8" minRefreshableVersion="5">
-    <extLst>
-      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
-        <x15:connection id="Table1" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_statisticstemplate.xlsxTable1"/>
-        </x15:connection>
-      </ext>
-    </extLst>
-  </connection>
-</connections>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
-    <t>Date</t>
+    <t>date</t>
   </si>
   <si>
-    <t>Store</t>
+    <t>storeName</t>
   </si>
   <si>
-    <t>Value</t>
+    <t>value</t>
   </si>
   <si>
     <t>Store A</t>
@@ -86,39 +46,35 @@
     <t>Store B</t>
   </si>
   <si>
-    <t>Store D</t>
+    <t>Row Labels</t>
   </si>
   <si>
-    <t>Store C</t>
+    <t>Grand Total</t>
   </si>
   <si>
-    <t>Store E</t>
+    <t>февр</t>
+  </si>
+  <si>
+    <t>май</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Sum of value</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -141,51 +97,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Unicode MS"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
@@ -215,6 +139,10 @@
       <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[statistics-template.xlsx]Dashboard!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
   <c:chart>
     <c:autoTitleDeleted val="0"/>
     <c:pivotFmts>
@@ -330,174 +258,6 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -509,7 +269,15 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>01.05.2026</c:v>
+            <c:strRef>
+              <c:f>Dashboard!$C$2:$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Store A</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -522,37 +290,37 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strLit>
-              <c:ptCount val="5"/>
-              <c:pt idx="0">
-                <c:v>Store A</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>Store B</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>Store C</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>Store D</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>Store E</c:v>
-              </c:pt>
-            </c:strLit>
+            <c:strRef>
+              <c:f>Dashboard!$B$4:$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>февр</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>май</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="5"/>
-              <c:pt idx="0">
-                <c:v>10</c:v>
-              </c:pt>
-            </c:numLit>
+            <c:numRef>
+              <c:f>Dashboard!$C$4:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D338-41F9-ABB2-7E084365A3DF}"/>
+              <c16:uniqueId val="{00000000-F26D-40DE-80A1-E5B4BC39E831}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -560,7 +328,15 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>02.05.2026</c:v>
+            <c:strRef>
+              <c:f>Dashboard!$D$2:$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Store B</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -573,190 +349,34 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strLit>
-              <c:ptCount val="5"/>
-              <c:pt idx="0">
-                <c:v>Store A</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>Store B</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>Store C</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>Store D</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>Store E</c:v>
-              </c:pt>
-            </c:strLit>
+            <c:strRef>
+              <c:f>Dashboard!$B$4:$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>февр</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>май</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="5"/>
-              <c:pt idx="1">
-                <c:v>10</c:v>
-              </c:pt>
-            </c:numLit>
+            <c:numRef>
+              <c:f>Dashboard!$D$4:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D338-41F9-ABB2-7E084365A3DF}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>03.05.2026</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strLit>
-              <c:ptCount val="5"/>
-              <c:pt idx="0">
-                <c:v>Store A</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>Store B</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>Store C</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>Store D</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>Store E</c:v>
-              </c:pt>
-            </c:strLit>
-          </c:cat>
-          <c:val>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="5"/>
-              <c:pt idx="3">
-                <c:v>10</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-D338-41F9-ABB2-7E084365A3DF}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:v>04.05.2026</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strLit>
-              <c:ptCount val="5"/>
-              <c:pt idx="0">
-                <c:v>Store A</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>Store B</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>Store C</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>Store D</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>Store E</c:v>
-              </c:pt>
-            </c:strLit>
-          </c:cat>
-          <c:val>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="5"/>
-              <c:pt idx="2">
-                <c:v>10</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-D338-41F9-ABB2-7E084365A3DF}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:v>05.05.2026</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strLit>
-              <c:ptCount val="5"/>
-              <c:pt idx="0">
-                <c:v>Store A</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>Store B</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>Store C</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>Store D</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>Store E</c:v>
-              </c:pt>
-            </c:strLit>
-          </c:cat>
-          <c:val>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="5"/>
-              <c:pt idx="4">
-                <c:v>10</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-D338-41F9-ABB2-7E084365A3DF}"/>
+              <c16:uniqueId val="{00000001-F26D-40DE-80A1-E5B4BC39E831}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -770,17 +390,17 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="717487343"/>
-        <c:axId val="717499343"/>
+        <c:axId val="1186237423"/>
+        <c:axId val="1186238383"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="717487343"/>
+        <c:axId val="1186237423"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -817,20 +437,15 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="717499343"/>
+        <c:crossAx val="1186238383"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{F40574EE-89B7-4290-83BB-5DA773EAF853}">
-            <c15:numFmt c:formatCode="General" c:sourceLinked="1"/>
-          </c:ext>
-        </c:extLst>
       </c:catAx>
       <c:valAx>
-        <c:axId val="717499343"/>
+        <c:axId val="1186238383"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -850,7 +465,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -881,14 +496,9 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="717487343"/>
+        <c:crossAx val="1186237423"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{F40574EE-89B7-4290-83BB-5DA773EAF853}">
-            <c15:numFmt c:formatCode="General" c:sourceLinked="1"/>
-          </c:ext>
-        </c:extLst>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -971,18 +581,14 @@
     <c:pageSetup/>
   </c:printSettings>
   <c:extLst>
-    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{723BEF56-08C2-4564-9609-F4CBC75E7E54}">
-      <c15:pivotSource>
-        <c15:name>[statistics-template.xlsx]PivotChartTable1</c15:name>
-        <c15:fmtId val="0"/>
-      </c15:pivotSource>
-      <c15:pivotOptions>
-        <c15:dropZoneFilter val="1"/>
-        <c15:dropZoneCategories val="1"/>
-        <c15:dropZoneData val="1"/>
-        <c15:dropZoneSeries val="1"/>
-        <c15:dropZonesVisible val="1"/>
-      </c15:pivotOptions>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
       <c16:pivotOptions16>
@@ -1540,23 +1146,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C54CECB-A6B6-FEEB-F5FA-F9EB3CBB767A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{234E57A7-1C09-1DFA-D6B4-051EE3E860D6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1578,162 +1184,904 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="LEPTOP" refreshedDate="46151.616328935183" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{15C8C742-E183-42EC-9AD9-7394C2C5E40D}">
-  <cacheSource type="external" connectionId="1">
-    <extLst>
-      <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{F057638F-6D5F-4e77-A914-E7F072B9BCA8}">
-        <x14:sourceConnection name="ThisWorkbookDataModel"/>
-      </ext>
-    </extLst>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="LEPTOP" refreshedDate="46151.645818865742" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{98353903-2A8B-4547-A70F-54389B1E7DDF}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1"/>
   </cacheSource>
-  <cacheFields count="3">
-    <cacheField name="[Table1].[Date].[Date]" caption="Date" numFmtId="0" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-01T00:00:00" maxDate="2026-05-06T00:00:00" count="5">
+  <cacheFields count="5">
+    <cacheField name="date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-02-02T00:00:00" maxDate="2026-05-03T00:00:00" count="3">
         <d v="2026-05-01T00:00:00"/>
         <d v="2026-05-02T00:00:00"/>
-        <d v="2026-05-03T00:00:00"/>
-        <d v="2026-05-04T00:00:00"/>
-        <d v="2026-05-05T00:00:00"/>
+        <d v="2026-02-02T00:00:00"/>
+      </sharedItems>
+      <fieldGroup par="4"/>
+    </cacheField>
+    <cacheField name="storeName" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Store A"/>
+        <s v="Store B"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Table1].[Store].[Store]" caption="Store" numFmtId="0" hierarchy="1" level="1">
-      <sharedItems count="5">
-        <s v="Store A"/>
-        <s v="Store B"/>
-        <s v="Store C"/>
-        <s v="Store D"/>
-        <s v="Store E"/>
-      </sharedItems>
+    <cacheField name="value" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="5" maxValue="15"/>
     </cacheField>
-    <cacheField name="[Measures].[Sum of Value]" caption="Sum of Value" numFmtId="0" hierarchy="5" level="32767"/>
+    <cacheField name="Days (date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="days" startDate="2026-02-02T00:00:00" endDate="2026-05-03T00:00:00"/>
+        <groupItems count="368">
+          <s v="&lt;02.02.2026"/>
+          <s v="01.янв"/>
+          <s v="02.янв"/>
+          <s v="03.янв"/>
+          <s v="04.янв"/>
+          <s v="05.янв"/>
+          <s v="06.янв"/>
+          <s v="07.янв"/>
+          <s v="08.янв"/>
+          <s v="09.янв"/>
+          <s v="10.янв"/>
+          <s v="11.янв"/>
+          <s v="12.янв"/>
+          <s v="13.янв"/>
+          <s v="14.янв"/>
+          <s v="15.янв"/>
+          <s v="16.янв"/>
+          <s v="17.янв"/>
+          <s v="18.янв"/>
+          <s v="19.янв"/>
+          <s v="20.янв"/>
+          <s v="21.янв"/>
+          <s v="22.янв"/>
+          <s v="23.янв"/>
+          <s v="24.янв"/>
+          <s v="25.янв"/>
+          <s v="26.янв"/>
+          <s v="27.янв"/>
+          <s v="28.янв"/>
+          <s v="29.янв"/>
+          <s v="30.янв"/>
+          <s v="31.янв"/>
+          <s v="01.февр"/>
+          <s v="02.февр"/>
+          <s v="03.февр"/>
+          <s v="04.февр"/>
+          <s v="05.февр"/>
+          <s v="06.февр"/>
+          <s v="07.февр"/>
+          <s v="08.февр"/>
+          <s v="09.февр"/>
+          <s v="10.февр"/>
+          <s v="11.февр"/>
+          <s v="12.февр"/>
+          <s v="13.февр"/>
+          <s v="14.февр"/>
+          <s v="15.февр"/>
+          <s v="16.февр"/>
+          <s v="17.февр"/>
+          <s v="18.февр"/>
+          <s v="19.февр"/>
+          <s v="20.февр"/>
+          <s v="21.февр"/>
+          <s v="22.февр"/>
+          <s v="23.февр"/>
+          <s v="24.февр"/>
+          <s v="25.февр"/>
+          <s v="26.февр"/>
+          <s v="27.февр"/>
+          <s v="28.февр"/>
+          <s v="29.февр"/>
+          <s v="01.март"/>
+          <s v="02.март"/>
+          <s v="03.март"/>
+          <s v="04.март"/>
+          <s v="05.март"/>
+          <s v="06.март"/>
+          <s v="07.март"/>
+          <s v="08.март"/>
+          <s v="09.март"/>
+          <s v="10.март"/>
+          <s v="11.март"/>
+          <s v="12.март"/>
+          <s v="13.март"/>
+          <s v="14.март"/>
+          <s v="15.март"/>
+          <s v="16.март"/>
+          <s v="17.март"/>
+          <s v="18.март"/>
+          <s v="19.март"/>
+          <s v="20.март"/>
+          <s v="21.март"/>
+          <s v="22.март"/>
+          <s v="23.март"/>
+          <s v="24.март"/>
+          <s v="25.март"/>
+          <s v="26.март"/>
+          <s v="27.март"/>
+          <s v="28.март"/>
+          <s v="29.март"/>
+          <s v="30.март"/>
+          <s v="31.март"/>
+          <s v="01.апр"/>
+          <s v="02.апр"/>
+          <s v="03.апр"/>
+          <s v="04.апр"/>
+          <s v="05.апр"/>
+          <s v="06.апр"/>
+          <s v="07.апр"/>
+          <s v="08.апр"/>
+          <s v="09.апр"/>
+          <s v="10.апр"/>
+          <s v="11.апр"/>
+          <s v="12.апр"/>
+          <s v="13.апр"/>
+          <s v="14.апр"/>
+          <s v="15.апр"/>
+          <s v="16.апр"/>
+          <s v="17.апр"/>
+          <s v="18.апр"/>
+          <s v="19.апр"/>
+          <s v="20.апр"/>
+          <s v="21.апр"/>
+          <s v="22.апр"/>
+          <s v="23.апр"/>
+          <s v="24.апр"/>
+          <s v="25.апр"/>
+          <s v="26.апр"/>
+          <s v="27.апр"/>
+          <s v="28.апр"/>
+          <s v="29.апр"/>
+          <s v="30.апр"/>
+          <s v="01.май"/>
+          <s v="02.май"/>
+          <s v="03.май"/>
+          <s v="04.май"/>
+          <s v="05.май"/>
+          <s v="06.май"/>
+          <s v="07.май"/>
+          <s v="08.май"/>
+          <s v="09.май"/>
+          <s v="10.май"/>
+          <s v="11.май"/>
+          <s v="12.май"/>
+          <s v="13.май"/>
+          <s v="14.май"/>
+          <s v="15.май"/>
+          <s v="16.май"/>
+          <s v="17.май"/>
+          <s v="18.май"/>
+          <s v="19.май"/>
+          <s v="20.май"/>
+          <s v="21.май"/>
+          <s v="22.май"/>
+          <s v="23.май"/>
+          <s v="24.май"/>
+          <s v="25.май"/>
+          <s v="26.май"/>
+          <s v="27.май"/>
+          <s v="28.май"/>
+          <s v="29.май"/>
+          <s v="30.май"/>
+          <s v="31.май"/>
+          <s v="01.июнь"/>
+          <s v="02.июнь"/>
+          <s v="03.июнь"/>
+          <s v="04.июнь"/>
+          <s v="05.июнь"/>
+          <s v="06.июнь"/>
+          <s v="07.июнь"/>
+          <s v="08.июнь"/>
+          <s v="09.июнь"/>
+          <s v="10.июнь"/>
+          <s v="11.июнь"/>
+          <s v="12.июнь"/>
+          <s v="13.июнь"/>
+          <s v="14.июнь"/>
+          <s v="15.июнь"/>
+          <s v="16.июнь"/>
+          <s v="17.июнь"/>
+          <s v="18.июнь"/>
+          <s v="19.июнь"/>
+          <s v="20.июнь"/>
+          <s v="21.июнь"/>
+          <s v="22.июнь"/>
+          <s v="23.июнь"/>
+          <s v="24.июнь"/>
+          <s v="25.июнь"/>
+          <s v="26.июнь"/>
+          <s v="27.июнь"/>
+          <s v="28.июнь"/>
+          <s v="29.июнь"/>
+          <s v="30.июнь"/>
+          <s v="01.июль"/>
+          <s v="02.июль"/>
+          <s v="03.июль"/>
+          <s v="04.июль"/>
+          <s v="05.июль"/>
+          <s v="06.июль"/>
+          <s v="07.июль"/>
+          <s v="08.июль"/>
+          <s v="09.июль"/>
+          <s v="10.июль"/>
+          <s v="11.июль"/>
+          <s v="12.июль"/>
+          <s v="13.июль"/>
+          <s v="14.июль"/>
+          <s v="15.июль"/>
+          <s v="16.июль"/>
+          <s v="17.июль"/>
+          <s v="18.июль"/>
+          <s v="19.июль"/>
+          <s v="20.июль"/>
+          <s v="21.июль"/>
+          <s v="22.июль"/>
+          <s v="23.июль"/>
+          <s v="24.июль"/>
+          <s v="25.июль"/>
+          <s v="26.июль"/>
+          <s v="27.июль"/>
+          <s v="28.июль"/>
+          <s v="29.июль"/>
+          <s v="30.июль"/>
+          <s v="31.июль"/>
+          <s v="01.авг"/>
+          <s v="02.авг"/>
+          <s v="03.авг"/>
+          <s v="04.авг"/>
+          <s v="05.авг"/>
+          <s v="06.авг"/>
+          <s v="07.авг"/>
+          <s v="08.авг"/>
+          <s v="09.авг"/>
+          <s v="10.авг"/>
+          <s v="11.авг"/>
+          <s v="12.авг"/>
+          <s v="13.авг"/>
+          <s v="14.авг"/>
+          <s v="15.авг"/>
+          <s v="16.авг"/>
+          <s v="17.авг"/>
+          <s v="18.авг"/>
+          <s v="19.авг"/>
+          <s v="20.авг"/>
+          <s v="21.авг"/>
+          <s v="22.авг"/>
+          <s v="23.авг"/>
+          <s v="24.авг"/>
+          <s v="25.авг"/>
+          <s v="26.авг"/>
+          <s v="27.авг"/>
+          <s v="28.авг"/>
+          <s v="29.авг"/>
+          <s v="30.авг"/>
+          <s v="31.авг"/>
+          <s v="01.сент"/>
+          <s v="02.сент"/>
+          <s v="03.сент"/>
+          <s v="04.сент"/>
+          <s v="05.сент"/>
+          <s v="06.сент"/>
+          <s v="07.сент"/>
+          <s v="08.сент"/>
+          <s v="09.сент"/>
+          <s v="10.сент"/>
+          <s v="11.сент"/>
+          <s v="12.сент"/>
+          <s v="13.сент"/>
+          <s v="14.сент"/>
+          <s v="15.сент"/>
+          <s v="16.сент"/>
+          <s v="17.сент"/>
+          <s v="18.сент"/>
+          <s v="19.сент"/>
+          <s v="20.сент"/>
+          <s v="21.сент"/>
+          <s v="22.сент"/>
+          <s v="23.сент"/>
+          <s v="24.сент"/>
+          <s v="25.сент"/>
+          <s v="26.сент"/>
+          <s v="27.сент"/>
+          <s v="28.сент"/>
+          <s v="29.сент"/>
+          <s v="30.сент"/>
+          <s v="01.окт"/>
+          <s v="02.окт"/>
+          <s v="03.окт"/>
+          <s v="04.окт"/>
+          <s v="05.окт"/>
+          <s v="06.окт"/>
+          <s v="07.окт"/>
+          <s v="08.окт"/>
+          <s v="09.окт"/>
+          <s v="10.окт"/>
+          <s v="11.окт"/>
+          <s v="12.окт"/>
+          <s v="13.окт"/>
+          <s v="14.окт"/>
+          <s v="15.окт"/>
+          <s v="16.окт"/>
+          <s v="17.окт"/>
+          <s v="18.окт"/>
+          <s v="19.окт"/>
+          <s v="20.окт"/>
+          <s v="21.окт"/>
+          <s v="22.окт"/>
+          <s v="23.окт"/>
+          <s v="24.окт"/>
+          <s v="25.окт"/>
+          <s v="26.окт"/>
+          <s v="27.окт"/>
+          <s v="28.окт"/>
+          <s v="29.окт"/>
+          <s v="30.окт"/>
+          <s v="31.окт"/>
+          <s v="01.нояб"/>
+          <s v="02.нояб"/>
+          <s v="03.нояб"/>
+          <s v="04.нояб"/>
+          <s v="05.нояб"/>
+          <s v="06.нояб"/>
+          <s v="07.нояб"/>
+          <s v="08.нояб"/>
+          <s v="09.нояб"/>
+          <s v="10.нояб"/>
+          <s v="11.нояб"/>
+          <s v="12.нояб"/>
+          <s v="13.нояб"/>
+          <s v="14.нояб"/>
+          <s v="15.нояб"/>
+          <s v="16.нояб"/>
+          <s v="17.нояб"/>
+          <s v="18.нояб"/>
+          <s v="19.нояб"/>
+          <s v="20.нояб"/>
+          <s v="21.нояб"/>
+          <s v="22.нояб"/>
+          <s v="23.нояб"/>
+          <s v="24.нояб"/>
+          <s v="25.нояб"/>
+          <s v="26.нояб"/>
+          <s v="27.нояб"/>
+          <s v="28.нояб"/>
+          <s v="29.нояб"/>
+          <s v="30.нояб"/>
+          <s v="01.дек"/>
+          <s v="02.дек"/>
+          <s v="03.дек"/>
+          <s v="04.дек"/>
+          <s v="05.дек"/>
+          <s v="06.дек"/>
+          <s v="07.дек"/>
+          <s v="08.дек"/>
+          <s v="09.дек"/>
+          <s v="10.дек"/>
+          <s v="11.дек"/>
+          <s v="12.дек"/>
+          <s v="13.дек"/>
+          <s v="14.дек"/>
+          <s v="15.дек"/>
+          <s v="16.дек"/>
+          <s v="17.дек"/>
+          <s v="18.дек"/>
+          <s v="19.дек"/>
+          <s v="20.дек"/>
+          <s v="21.дек"/>
+          <s v="22.дек"/>
+          <s v="23.дек"/>
+          <s v="24.дек"/>
+          <s v="25.дек"/>
+          <s v="26.дек"/>
+          <s v="27.дек"/>
+          <s v="28.дек"/>
+          <s v="29.дек"/>
+          <s v="30.дек"/>
+          <s v="31.дек"/>
+          <s v="&gt;03.05.2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Months (date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="months" startDate="2026-02-02T00:00:00" endDate="2026-05-03T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;02.02.2026"/>
+          <s v="янв"/>
+          <s v="февр"/>
+          <s v="март"/>
+          <s v="апр"/>
+          <s v="май"/>
+          <s v="июнь"/>
+          <s v="июль"/>
+          <s v="авг"/>
+          <s v="сент"/>
+          <s v="окт"/>
+          <s v="нояб"/>
+          <s v="дек"/>
+          <s v="&gt;03.05.2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
   </cacheFields>
-  <cacheHierarchies count="6">
-    <cacheHierarchy uniqueName="[Table1].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Date].[All]" allUniqueName="[Table1].[Date].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Store]" caption="Store" attribute="1" defaultMemberUniqueName="[Table1].[Store].[All]" allUniqueName="[Table1].[Store].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Value]" caption="Value" attribute="1" defaultMemberUniqueName="[Table1].[Value].[All]" allUniqueName="[Table1].[Value].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Value]" caption="Sum of Value" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="2"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Table1" caption="Table1"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition pivotCacheId="1141564169" supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{ABF5C744-AB39-4b91-8756-CFA1BBC848D5}">
-      <x15:pivotCacheIdVersion cacheIdSupportedVersion="6" cacheIdCreatedVersion="7"/>
+      <x14:pivotCacheDefinition/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="3">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="5"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E33B9B4B-8D4E-4057-BE4B-33F1A8148C91}" name="PivotChartTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A1:G8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F22A8228-6C17-4FC8-AA82-F0AF77656A78}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="B2:E6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="4">
+        <item x="2"/>
         <item x="0"/>
         <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="5">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
         <item x="0"/>
         <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
-  <rowFields count="1">
+  <rowFields count="3">
+    <field x="4"/>
+    <field x="3"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
     <field x="1"/>
-  </rowFields>
-  <rowItems count="6">
+  </colFields>
+  <colItems count="3">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
     </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
     <i t="grand">
       <x/>
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Value" fld="2" baseField="0" baseItem="0"/>
+    <dataField name="Sum of value" fld="2" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="5">
+  <chartFormats count="4">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" count="1" selected="0">
+          <reference field="1" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
@@ -1742,7 +2090,7 @@
     <chartFormat chart="0" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" count="1" selected="0">
+          <reference field="1" count="1" selected="0">
             <x v="1"/>
           </reference>
         </references>
@@ -1750,193 +2098,48 @@
     </chartFormat>
     <chartFormat chart="0" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1" selected="0">
-            <x v="2"/>
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
     <chartFormat chart="0" format="3" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1" selected="0">
-            <x v="3"/>
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
           </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1" selected="0">
-            <x v="4"/>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="6">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="1"/>
-  </rowHierarchiesUsage>
-  <colHierarchiesUsage count="1">
-    <colHierarchyUsage hierarchyUsage="0"/>
-  </colHierarchiesUsage>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{44433962-1CF7-4059-B4EE-95C3D5FFCF73}">
-      <x15:pivotTableData rowCount="6" columnCount="6" cacheId="1141564169">
-        <x15:pivotRow count="6">
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-        </x15:pivotRow>
-        <x15:pivotRow count="6">
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-        </x15:pivotRow>
-        <x15:pivotRow count="6">
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-        </x15:pivotRow>
-        <x15:pivotRow count="6">
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-        </x15:pivotRow>
-        <x15:pivotRow count="6">
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c t="e">
-            <x15:v/>
-          </x15:c>
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-        </x15:pivotRow>
-        <x15:pivotRow count="6">
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-          <x15:c>
-            <x15:v>10</x15:v>
-          </x15:c>
-          <x15:c>
-            <x15:v>50</x15:v>
-          </x15:c>
-        </x15:pivotRow>
-      </x15:pivotTableData>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_statistics-template.xlsx!Table1">
-        <x15:activeTabTopLevelEntity name="[Table1]"/>
-      </x15:pivotTableUISettings>
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+      <xpdl:pivotTableDefinition16/>
     </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6945AE30-B438-41B7-8372-3673D5F80A21}" name="Table1" displayName="Table1" ref="A1:C6" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:C6" xr:uid="{6945AE30-B438-41B7-8372-3673D5F80A21}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DC1F3EAB-68DD-416F-BA26-9D8578AA8CD4}" name="Table1" displayName="Table1" ref="A1:C4" totalsRowShown="0">
+  <autoFilter ref="A1:C4" xr:uid="{DC1F3EAB-68DD-416F-BA26-9D8578AA8CD4}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{4542B96E-9A1D-48A2-A77A-9A974821E374}" name="Date" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{C1BFA78E-6DED-41EC-9A2A-616042B0A4CA}" name="Store"/>
-    <tableColumn id="3" xr3:uid="{E3FBB4EA-7635-498C-81E1-443A8834DBDF}" name="Value" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{4DA45ABD-EDF7-4F94-8945-7094B804E3A7}" name="date" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{D2256635-0CD0-487F-8BB3-6A4826CDED94}" name="storeName"/>
+    <tableColumn id="3" xr3:uid="{92E1B826-965A-470B-86ED-688DFF670D35}" name="value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2205,87 +2408,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D12B7D8E-7440-4106-951F-5E4788909599}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.77734375" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
         <v>46143</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <v>46144</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3">
-        <v>10</v>
+      <c r="C3">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2">
-        <v>46145</v>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>46055</v>
       </c>
       <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
         <v>5</v>
-      </c>
-      <c r="C4" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2">
-        <v>46146</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2">
-        <v>46147</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2294,4 +2466,83 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EF0224D-086C-4382-8DF5-9912B65509DB}">
+  <dimension ref="B2:E6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4">
+        <v>10</v>
+      </c>
+      <c r="D5" s="4">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4">
+        <v>15</v>
+      </c>
+      <c r="E6" s="4">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>